--- a/data/trans_dic/IP31KM05_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM05_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>80,19%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>65,57; 82,33</t>
+          <t>75,69; 88,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>76,13; 88,52</t>
+          <t>69,72; 84,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74,0; 84,34</t>
+          <t>74,94; 84,59</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,34%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>79,94; 91,64</t>
+          <t>74,12; 87,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>72,98; 88,35</t>
+          <t>79,42; 91,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78,94; 88,41</t>
+          <t>79,26; 88,5</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>78,95%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>64,3; 86,03</t>
+          <t>71,01; 88,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>66,4; 86,49</t>
+          <t>62,91; 86,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>68,43; 83,33</t>
+          <t>70,42; 85,05</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>81,57%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>72,43; 86,76</t>
+          <t>82,02; 90,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>81,5; 90,13</t>
+          <t>70,29; 81,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78,87; 86,47</t>
+          <t>78,05; 84,65</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>78,58%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>75,18; 87,66</t>
+          <t>67,92; 82,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>66,14; 80,94</t>
+          <t>75,58; 87,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72,52; 82,56</t>
+          <t>73,89; 83,13</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>85,02%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>76,46; 90,92</t>
+          <t>74,99; 92,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>74,27; 91,54</t>
+          <t>76,15; 90,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>78,18; 89,66</t>
+          <t>78,91; 89,4</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,27%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>77,37; 83,65</t>
+          <t>79,41; 84,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>78,59; 84,19</t>
+          <t>77,01; 82,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78,93; 83,14</t>
+          <t>79,31; 83,09</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>119</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>76779</t>
+          <t>99949</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>112325</t>
+          <t>77718</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>189104</t>
+          <t>177667</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>66690; 83741</t>
+          <t>91748; 107782</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>102909; 119660</t>
+          <t>69958; 84558</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>175288; 199786</t>
+          <t>166037; 187416</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>118</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>80908</t>
+          <t>73696</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>76293</t>
+          <t>82585</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>157202</t>
+          <t>156281</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>74658; 85588</t>
+          <t>66623; 79044</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>68393; 82787</t>
+          <t>75770; 87442</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>147694; 165408</t>
+          <t>146854; 163990</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>56</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>45353</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48514</t>
+          <t>39801</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>86650</t>
+          <t>85154</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>32207; 43090</t>
+          <t>39657; 49484</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>41392; 53910</t>
+          <t>32717; 44772</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>76935; 93676</t>
+          <t>75946; 91734</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>208</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>170118</t>
+          <t>171060</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>183761</t>
+          <t>133979</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>353880</t>
+          <t>305040</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>156110; 186991</t>
+          <t>161844; 178769</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>173309; 191669</t>
+          <t>124166; 143178</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>337732; 370272</t>
+          <t>291887; 316537</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>139</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>95307</t>
+          <t>110015</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>118736</t>
+          <t>95107</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>214043</t>
+          <t>205122</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>86844; 101253</t>
+          <t>98882; 119644</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>105475; 129075</t>
+          <t>87273; 101028</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>199417; 227008</t>
+          <t>192883; 217023</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>83</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>58256</t>
+          <t>56431</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>58456</t>
+          <t>59376</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>116711</t>
+          <t>115808</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>52675; 62636</t>
+          <t>49393; 60931</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>51266; 63192</t>
+          <t>53575; 63661</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>107835; 123666</t>
+          <t>107485; 121778</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>723</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>756</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>519505</t>
+          <t>556505</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>598085</t>
+          <t>488567</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1117589</t>
+          <t>1045072</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>499111; 539624</t>
+          <t>536581; 572998</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>575557; 616575</t>
+          <t>469959; 504849</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1087303; 1145215</t>
+          <t>1019837; 1068510</t>
         </is>
       </c>
     </row>
